--- a/outputs/scoring_method_L1.xlsx
+++ b/outputs/scoring_method_L1.xlsx
@@ -544,7 +544,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-08</t>
+          <t>Generated: 2026-07-09</t>
         </is>
       </c>
     </row>
